--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484142_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484142_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6336</v>
+        <v>3.6432</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0912</v>
+        <v>2.9325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5424</v>
+        <v>0.7107</v>
       </c>
       <c r="G2" t="n">
         <v>3.8897</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1407</v>
+        <v>0.1503</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0625</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.2465</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.076</v>
+        <v>0.2723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6244</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4516</v>
+        <v>0.3394</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4088</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4216</v>
+        <v>0.6178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9807</v>
+        <v>0.2892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4409</v>
+        <v>0.3287</v>
       </c>
       <c r="V3" t="n">
         <v>-0.532</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.6383</v>
+        <v>-3.0253</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.6504</v>
+        <v>-2.9532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.012</v>
+        <v>-0.0721</v>
       </c>
       <c r="G4" t="n">
         <v>-3.0446</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5776</v>
+        <v>0.0354</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7991</v>
+        <v>-0.102</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2216</v>
+        <v>0.1374</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2065</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.5983</v>
+        <v>-3.2022</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.7769</v>
+        <v>-4.7736</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1786</v>
+        <v>1.5714</v>
       </c>
       <c r="G5" t="n">
         <v>-4.1857</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9997</v>
+        <v>-0.6036</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4963</v>
+        <v>-0.493</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5034</v>
+        <v>-0.1106</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>M. NINOT PEDROSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.7914</v>
+        <v>-4.941</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.7649</v>
+        <v>-1.4013</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0264</v>
+        <v>-3.5397</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.6984</v>
+        <v>-2.6008</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2948</v>
+        <v>-0.524</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.4036</v>
+        <v>-2.0768</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7723</v>
+        <v>0.2484</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9083</v>
+        <v>1.0038</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.6806</v>
+        <v>-0.7554</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.9261</v>
+        <v>-2.8492</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2031</v>
+        <v>-1.5278</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.723</v>
+        <v>-1.3214</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9782999999999999</v>
+        <v>-0.4548</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0625</v>
+        <v>-0.9238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0713</v>
+        <v>-2.6789</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0713</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.8649</v>
+        <v>-5.4778</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5853</v>
+        <v>-3.9463</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2795</v>
+        <v>-1.5314</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7278</v>
+        <v>-5.6984</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3105</v>
+        <v>-1.2948</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4173</v>
+        <v>-4.4036</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.136</v>
+        <v>-1.7723</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1762</v>
+        <v>0.9083</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>-2.6806</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5918</v>
+        <v>-3.9261</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1343</v>
+        <v>-2.2031</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4574</v>
+        <v>-1.723</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.2919</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3119</v>
+        <v>-0.1189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2652</v>
+        <v>0.4108</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.532</v>
+        <v>-0.0713</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NINOT PEDROSA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.5478</v>
+        <v>-5.5269</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0362</v>
+        <v>-3.1352</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5116</v>
+        <v>-2.3917</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6008</v>
+        <v>-2.7278</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.524</v>
+        <v>-1.3105</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0768</v>
+        <v>-1.4173</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2484</v>
+        <v>-0.136</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0038</v>
+        <v>-0.1762</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7554</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8492</v>
+        <v>-2.5918</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5278</v>
+        <v>-1.1343</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3214</v>
+        <v>-1.4574</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R8" t="n">
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0616</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5586</v>
+        <v>-0.238</v>
       </c>
       <c r="U8" t="n">
-        <v>0.497</v>
+        <v>0.153</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6789</v>
+        <v>-0.532</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9449</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1784</v>
+        <v>-6.0274</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7789</v>
+        <v>-4.6741</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3995</v>
+        <v>-1.3533</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.878</v>
+        <v>-6.2853</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3258</v>
+        <v>-1.6433</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5522</v>
+        <v>-4.642</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5567</v>
+        <v>-3.6984</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1963</v>
+        <v>-0.3778</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3604</v>
+        <v>-3.3207</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3213</v>
+        <v>-2.5869</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1295</v>
+        <v>-1.2655</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1918</v>
+        <v>-1.3214</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3004</v>
+        <v>-0.2579</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5044</v>
+        <v>-0.5157</v>
       </c>
       <c r="U9" t="n">
-        <v>0.204</v>
+        <v>0.2579</v>
       </c>
       <c r="V9" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="X9" t="n">
         <v>-1.2065</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.4724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.9031</v>
+        <v>-6.1784</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2692</v>
+        <v>-3.7789</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6338</v>
+        <v>-2.3995</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.2853</v>
+        <v>-3.878</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6433</v>
+        <v>-1.3258</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.642</v>
+        <v>-2.5522</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.6984</v>
+        <v>-1.5567</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3778</v>
+        <v>-0.1963</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.3207</v>
+        <v>-1.3604</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5869</v>
+        <v>-2.3213</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2655</v>
+        <v>-1.1295</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3214</v>
+        <v>-1.1918</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.1903</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.1822</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.1336</v>
+        <v>-0.3004</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1109</v>
+        <v>-0.5044</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0227</v>
+        <v>0.204</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6745</v>
+        <v>-1.2065</v>
       </c>
       <c r="W10" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-31.8126</v>
+        <v>-30.4635</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.1462</v>
+        <v>-21.7972</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.6662</v>
+        <v>-8.666199999999998</v>
       </c>
       <c r="G11" t="n">
         <v>-24.9397</v>
@@ -1312,13 +1312,13 @@
         <v>17.8546</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9552</v>
+        <v>-0.6063000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.051699999999999</v>
+        <v>-2.7028</v>
       </c>
       <c r="U11" t="n">
-        <v>2.0966</v>
+        <v>2.0967</v>
       </c>
       <c r="V11" t="n">
         <v>-6.9017</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.940099999999999</v>
+        <v>8.3619</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8674</v>
+        <v>5.1532</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0726</v>
+        <v>3.2087</v>
       </c>
       <c r="G12" t="n">
         <v>2.47</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9182</v>
+        <v>0.3401</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6122</v>
+        <v>-0.102</v>
       </c>
       <c r="U12" t="n">
-        <v>0.306</v>
+        <v>0.442</v>
       </c>
       <c r="V12" t="n">
         <v>4.5599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7532</v>
+        <v>8.1775</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4791</v>
+        <v>4.6832</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2741</v>
+        <v>3.4943</v>
       </c>
       <c r="G13" t="n">
         <v>4.4405</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5844</v>
+        <v>-0.1602</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0277</v>
+        <v>0.2479</v>
       </c>
       <c r="V13" t="n">
         <v>4.2939</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8861</v>
+        <v>5.3503</v>
       </c>
       <c r="E14" t="n">
-        <v>2.189</v>
+        <v>2.5971</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6971</v>
+        <v>2.7532</v>
       </c>
       <c r="G14" t="n">
         <v>4.1014</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.0766</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7991</v>
+        <v>-0.391</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2583</v>
+        <v>0.3145</v>
       </c>
       <c r="V14" t="n">
         <v>0.532</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2237</v>
+        <v>3.2498</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8491</v>
+        <v>1.9396</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3745</v>
+        <v>1.3102</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2959</v>
+        <v>2.0312</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0208</v>
+        <v>-0.3228</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2751</v>
+        <v>2.354</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3718</v>
+        <v>1.951</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6061</v>
+        <v>0.1411</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.8098</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9241</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5853</v>
+        <v>-0.4639</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5094</v>
+        <v>0.5442</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4039</v>
+        <v>0.2267</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.0113</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3358</v>
+        <v>0.238</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.881</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0138</v>
+        <v>2.4304</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5319</v>
+        <v>0.645</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4819</v>
+        <v>1.7854</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8979</v>
+        <v>4.2959</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0183</v>
+        <v>2.0208</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9162</v>
+        <v>2.2751</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8063</v>
+        <v>3.3718</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5592</v>
+        <v>2.6061</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3655</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0916</v>
+        <v>0.9241</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.459</v>
+        <v>-0.5853</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5507</v>
+        <v>1.5094</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5207</v>
+        <v>0.6107</v>
       </c>
       <c r="T16" t="n">
-        <v>0.924</v>
+        <v>-0.136</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5968</v>
+        <v>0.7466</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9234</v>
+        <v>2.3457</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8376</v>
+        <v>0.8205</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0857</v>
+        <v>1.5252</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0312</v>
+        <v>2.9041</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3228</v>
+        <v>-0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>2.354</v>
+        <v>2.9448</v>
       </c>
       <c r="J17" t="n">
-        <v>1.951</v>
+        <v>3.0141</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1411</v>
+        <v>0.4839</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8098</v>
+        <v>2.5302</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4639</v>
+        <v>-0.5246</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5442</v>
+        <v>0.4146</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0998</v>
+        <v>0.4336</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1133</v>
+        <v>-0.2097</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0136</v>
+        <v>0.6433</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0515</v>
+        <v>2.0471</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7185</v>
+        <v>0.8177</v>
       </c>
       <c r="F18" t="n">
-        <v>1.333</v>
+        <v>1.2294</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9041</v>
+        <v>0.8979</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0407</v>
+        <v>-1.0183</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9448</v>
+        <v>1.9162</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0141</v>
+        <v>0.8063</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4839</v>
+        <v>-0.5592</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5302</v>
+        <v>1.3655</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.11</v>
+        <v>0.0916</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5246</v>
+        <v>-0.459</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4146</v>
+        <v>0.5507</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1394</v>
+        <v>0.554</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3117</v>
+        <v>0.2098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4511</v>
+        <v>0.3443</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6102</v>
+        <v>1.593</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.31</v>
+        <v>-2.7999</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9202</v>
+        <v>4.3929</v>
       </c>
       <c r="G19" t="n">
         <v>3.3219</v>
@@ -1936,13 +1936,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1246</v>
+        <v>-0.1417</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.4874</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1271</v>
+        <v>0.3456</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2885</v>
+        <v>0.416</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2161</v>
+        <v>-1.808</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5045</v>
+        <v>2.224</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7143</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.34</v>
+        <v>0.4676</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8105</v>
+        <v>-0.4024</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1505</v>
+        <v>0.87</v>
       </c>
       <c r="V20" t="n">
         <v>0.266</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0213</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.9568</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6294</v>
+        <v>0.9661</v>
       </c>
       <c r="G21" t="n">
         <v>2.1745</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1848</v>
+        <v>0.2154</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4422</v>
+        <v>0.1361</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2574</v>
+        <v>0.0793</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8566</v>
+        <v>-1.4884</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6296</v>
+        <v>-2.4256</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7731</v>
+        <v>0.9372</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9834000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2024</v>
+        <v>0.1658</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2964</v>
+        <v>0.4605</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8692</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>31.8126</v>
+        <v>32.4926</v>
       </c>
       <c r="E23" t="n">
-        <v>8.6662</v>
+        <v>8.666</v>
       </c>
       <c r="F23" t="n">
-        <v>23.1461</v>
+        <v>23.8266</v>
       </c>
       <c r="G23" t="n">
         <v>24.9397</v>
@@ -2233,7 +2233,7 @@
         <v>5.422899999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.205300000000001</v>
+        <v>-6.205299999999999</v>
       </c>
       <c r="O23" t="n">
         <v>11.6283</v>
@@ -2248,13 +2248,13 @@
         <v>15.8707</v>
       </c>
       <c r="S23" t="n">
-        <v>1.955</v>
+        <v>2.6354</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.0965</v>
+        <v>-2.0966</v>
       </c>
       <c r="U23" t="n">
-        <v>4.051699999999999</v>
+        <v>4.731999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>6.901599999999999</v>
